--- a/data.xlsx
+++ b/data.xlsx
@@ -1,189 +1,76 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SchoolSM\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8887830A-CA65-443C-9135-69A36657D49D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{66610923-87E5-474C-A92E-6149D0BA8918}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ថ្នាក់រៀន" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ថ្នាក់រៀន" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="duty" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
-  <si>
-    <t>7A</t>
-  </si>
-  <si>
-    <t>7B</t>
-  </si>
-  <si>
-    <t>7C</t>
-  </si>
-  <si>
-    <t>7D</t>
-  </si>
-  <si>
-    <t>7E</t>
-  </si>
-  <si>
-    <t>8A</t>
-  </si>
-  <si>
-    <t>8B</t>
-  </si>
-  <si>
-    <t>8C</t>
-  </si>
-  <si>
-    <t>8D</t>
-  </si>
-  <si>
-    <t>9A</t>
-  </si>
-  <si>
-    <t>9B</t>
-  </si>
-  <si>
-    <t>9C</t>
-  </si>
-  <si>
-    <t>9D</t>
-  </si>
-  <si>
-    <t>10A</t>
-  </si>
-  <si>
-    <t>10B</t>
-  </si>
-  <si>
-    <t>10C</t>
-  </si>
-  <si>
-    <t>10D</t>
-  </si>
-  <si>
-    <t>10E</t>
-  </si>
-  <si>
-    <t>10F</t>
-  </si>
-  <si>
-    <t>10G</t>
-  </si>
-  <si>
-    <t>10H</t>
-  </si>
-  <si>
-    <t>10I</t>
-  </si>
-  <si>
-    <t>11A</t>
-  </si>
-  <si>
-    <t>11B</t>
-  </si>
-  <si>
-    <t>11C</t>
-  </si>
-  <si>
-    <t>11D</t>
-  </si>
-  <si>
-    <t>11E</t>
-  </si>
-  <si>
-    <t>11F</t>
-  </si>
-  <si>
-    <t>11G</t>
-  </si>
-  <si>
-    <t>11H</t>
-  </si>
-  <si>
-    <t>11I</t>
-  </si>
-  <si>
-    <t>12A</t>
-  </si>
-  <si>
-    <t>12B</t>
-  </si>
-  <si>
-    <t>12C</t>
-  </si>
-  <si>
-    <t>12D</t>
-  </si>
-  <si>
-    <t>12E</t>
-  </si>
-  <si>
-    <t>12F</t>
-  </si>
-  <si>
-    <t>12G</t>
-  </si>
-  <si>
-    <t>12H</t>
-  </si>
-  <si>
-    <t>12I</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="9">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Khmer OS"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Khmer OS"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Khmer OS"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Khmer OS"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Khmer OS"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Khmer OS"/>
+      <color theme="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Khmer OS"/>
+      <b val="1"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -194,8 +81,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.7999206518753624"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -218,29 +111,194 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color auto="1"/>
+      </left>
+      <right style="double">
+        <color auto="1"/>
+      </right>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom style="double">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -560,131 +618,3092 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AEB3756-6132-4806-9834-934C73BE4804}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:AN1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>7A</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>7B</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>7C</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>7D</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>7E</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>8A</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>8B</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>8C</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>8D</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>9A</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>9B</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>9C</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>9D</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>10A</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>10B</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>10C</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>10D</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>10E</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>10F</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>10G</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>10H</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>10I</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>11A</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>11B</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>11C</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>11D</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>11E</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>11F</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>11G</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>11H</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>11I</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>12A</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>12B</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>12C</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>12D</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>12E</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>12F</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>12G</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>12H</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>12I</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E116"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="10.88671875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="17.5546875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="22.6640625" bestFit="1" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="33" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>លរ</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>និម្មិតសញ្ញា</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>គោត្តនាម និង​ នាម</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ភេទ </t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>បង្រៀនថ្នាក់</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="25.8" customHeight="1" thickTop="1">
+      <c r="A2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>កាន ដាវី</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>7ABCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25.2" customHeight="1">
+      <c r="A3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>សា ប៊ុនថន</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>8ABCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25.2" customHeight="1">
+      <c r="A4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>យ៉ន ណារ៉ា</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>9ABCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25.2" customHeight="1">
+      <c r="A5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>ផេង លាងឃន</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>10DFH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="25.2" customHeight="1">
+      <c r="A6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>លឿង រក្សា</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>10CEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="25.2" customHeight="1">
+      <c r="A7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>ឡុច សាវិន</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>11I12EFGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="25.2" customHeight="1">
+      <c r="A8" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>យ៉ន សីហា</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>11FGH10I</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="25.2" customHeight="1">
+      <c r="A9" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>សេង សុសៅគន្ធ</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>7E11AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="25.2" customHeight="1">
+      <c r="A10" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>M9</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>ប៊ុន ឡាង</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>11BCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="25.2" customHeight="1">
+      <c r="A11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>សួន ច័ន្ទសុធី</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>10B12AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="25.2" customHeight="1">
+      <c r="A12" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>ផាត់ ស្រ៊ុន</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>10A12CDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="25.2" customHeight="1">
+      <c r="A13" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>ផល ឌីណា</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>7ABCDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="25.2" customHeight="1">
+      <c r="A14" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>ណុំ ស្រីណែត</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>8ABCD9ABCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="25.2" customHeight="1">
+      <c r="A15" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>សុង ភ័ស</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>10ABCDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="25.2" customHeight="1">
+      <c r="A16" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>កែវ សុគន្ធារី</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>10FGHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="25.2" customHeight="1">
+      <c r="A17" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>សាន់ កឿន</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>11BDEFGHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="25.2" customHeight="1">
+      <c r="A18" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>ជួង សុភ័ក្រ</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>11AC12AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="25.2" customHeight="1">
+      <c r="A19" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>វិន ភារុន</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>12CDEFGHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="25.2" customHeight="1">
+      <c r="A20" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>ដុក ណាសួន</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>7ABCDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="25.2" customHeight="1">
+      <c r="A21" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>ឯក អមរា</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>8ABCD9ABCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="25.2" customHeight="1">
+      <c r="A22" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>គង់ ម៉ានិន</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>10DI11BD</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="25.2" customHeight="1">
+      <c r="A23" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>ហន ស៊ីដារ៉ា</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>11EFGHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="25.2" customHeight="1">
+      <c r="A24" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>ពៅ ស៊ីនាង</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>10ABCEFGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="25.2" customHeight="1">
+      <c r="A25" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>បូ កញ្ញា</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>11AC12AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="25.2" customHeight="1">
+      <c r="A26" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>ក្រឹង ចន្ថា</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>12CDEFGHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="25.2" customHeight="1">
+      <c r="A27" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>សំ ពិសី</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>7ABCD9ABCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="25.2" customHeight="1">
+      <c r="A28" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>ជៃ ស្រីពៅ</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>10BCDEFGHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="25.2" customHeight="1">
+      <c r="A29" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>អ៊ឹម សំអុល</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>11AG12BGHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="25.2" customHeight="1">
+      <c r="A30" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>អ៊ិន ឆាយ</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>10A11BCDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="25.2" customHeight="1">
+      <c r="A31" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>ហៀង សេងហៃ</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>12ACDEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="25.2" customHeight="1">
+      <c r="A32" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>ឈឿន លីឆាយ</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>7E8ABCD11FHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="25.2" customHeight="1">
+      <c r="A33" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>ES1</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>វ៉ាន់ ម៉ាលីស</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>7ABCDE8ABCD9ABCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="25.2" customHeight="1">
+      <c r="A34" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>ES2</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>ហេង សានសុផានី</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>10ABCDEFGHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="25.2" customHeight="1">
+      <c r="A35" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>ES3</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>មូល គន្ធា</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>11ABCDEFGHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="25.2" customHeight="1">
+      <c r="A36" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>ES4</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>សុខ ស្រីនាង</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>12ABCDEFGHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="25.2" customHeight="1">
+      <c r="A37" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>សុន វាសនា</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>8ABCD9ABCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="25.2" customHeight="1">
+      <c r="A38" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>ឈាង ចាន់រ៉ា</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>10BCDEFGHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="25.2" customHeight="1">
+      <c r="A39" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>សួរ ចន្ទ្រា</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>7ABCDE11BCDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="25.2" customHeight="1">
+      <c r="A40" s="5" t="n">
         <v>39</v>
       </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>ឃឹម ស្រស់</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>11FG12ABDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="25.2" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>អេង រតនា</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>10A12CFGHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="25.2" customHeight="1">
+      <c r="A42" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>H6</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>ស៊ុំ វ៉េង</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>11AHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="25.2" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>I9G1</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>ទឹម ប៊ុនធន</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>7ABCDE8ABCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="25.2" customHeight="1">
+      <c r="A44" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>ចេង បុណ្ណវេទ</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>7ABCDE9ABCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="25.2" customHeight="1">
+      <c r="A45" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>ហេង កន្យា</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>10BCDEFGHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="25.2" customHeight="1">
+      <c r="A46" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>ជួ សូរីយា</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>11AB12DGHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="25.2" customHeight="1">
+      <c r="A47" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>សួន ស្រីរ័ត្ន</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>11CDEFGHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="25.2" customHeight="1">
+      <c r="A48" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>សុទ្ធ ចរិយា</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>10A12ABCEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="25.2" customHeight="1">
+      <c r="A49" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>ប៊ុន សម្បត្តិ</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>12ABCDEFGHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="25.2" customHeight="1">
+      <c r="A50" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>EC2</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>ពូន រចនា</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>11EFGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="25.2" customHeight="1">
+      <c r="A51" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>EC3</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>ហ៊ូ រ៉ន</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>11ABCDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="25.2" customHeight="1">
+      <c r="A52" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>He1</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>យ៉េន ចាន់នី</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>7ABCDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="25.2" customHeight="1">
+      <c r="A53" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>He2</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>យ៉េន ចាន់ណាក់</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>8ABCD9ABCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="25.2" customHeight="1">
+      <c r="A54" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>He3</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>ហេង សានម៉ូណាវី</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>10ABCDG</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="25.2" customHeight="1">
+      <c r="A55" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>He4</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>សែត រុនស្រី</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>10FHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="25.2" customHeight="1">
+      <c r="A56" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>I1</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>ពឺន ពិដោរ</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>8ABCD9ABCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="25.2" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>I2</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>ឆេង សុដានី</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>10CDEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="25.2" customHeight="1">
+      <c r="A58" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>I3</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>គង់ សម្បត្តិ</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>10BGHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="25.2" customHeight="1">
+      <c r="A59" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>I4</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>អាន ចាន់ថា</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>10A12ABCG</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="25.2" customHeight="1">
+      <c r="A60" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>I5</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>យ៉ាង សុផាន</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>11B12DEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="25.2" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>I6</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>សូកាន លក្ខិណា</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>11FI12HI</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="25.2" customHeight="1">
+      <c r="A62" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>I7</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>ផន កុសល</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>11ACDEGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="25.2" customHeight="1">
+      <c r="A63" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>យូ ម៉ាលីស</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>8BCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="25.2" customHeight="1">
+      <c r="A64" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>ឃុត បូរាមី</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>7CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="25.2" customHeight="1">
+      <c r="A65" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>ជឹង សុខចាន់</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>7AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="25.2" customHeight="1">
+      <c r="A66" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>K4</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>ប៉ន ផល្លី</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>9BCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="25.2" customHeight="1">
+      <c r="A67" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>K5</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>ប្រាក់ សារិន</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>8A9A</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="25.2" customHeight="1">
+      <c r="A68" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>ហួត លក្ខិណា</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>10EH</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="25.2" customHeight="1">
+      <c r="A69" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>K7</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>សុន ឌីម៉ង់</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>10BCF</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="25.2" customHeight="1">
+      <c r="A70" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>K8</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>ដួង ពិសេស</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>10DI</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="25.2" customHeight="1">
+      <c r="A71" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>K9</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>ដួង ពិសាល</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>11G12EI</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="25.2" customHeight="1">
+      <c r="A72" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>K10</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>មាស ស្រីលក្ខ័</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>7D10AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="25.2" customHeight="1">
+      <c r="A73" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>K11</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>ណុប វ៉ាង</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>12ACH</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="25.2" customHeight="1">
+      <c r="A74" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>K12</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>ខឹម សុផា</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>11CEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="25.2" customHeight="1">
+      <c r="A75" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>K13</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>ហេង  ឃាង</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>12FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="25.2" customHeight="1">
+      <c r="A76" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>K14</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>លន ស្រីលក្ខ័</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>11B12D</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="25.2" customHeight="1">
+      <c r="A77" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>K15</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>ខៀវ ខេមរិន្ទ</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>11ADHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="25.2" customHeight="1">
+      <c r="A78" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>K16</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>គាន  ហ៊ឺ</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>12B</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="25.2" customHeight="1">
+      <c r="A79" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>ចាន់  ធី</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>7ABCDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="25.2" customHeight="1">
+      <c r="A80" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>អោម សុខុម</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>8ABCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="25.2" customHeight="1">
+      <c r="A81" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>អ៊ុយ វាសនា</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 9ABCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="25.2" customHeight="1">
+      <c r="A82" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>ឃុន សុម៉ាឡា</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>10AEGI</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="25.2" customHeight="1">
+      <c r="A83" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>E5</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>ថោង ធីតា</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>10BCDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="25.2" customHeight="1">
+      <c r="A84" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>E6</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>ទិត សោម៉នវីរៈ</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>11ABCDGHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="25.2" customHeight="1">
+      <c r="A85" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>E7</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>អៀ សេរីពង្ស</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>11EF12ACDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="25.2" customHeight="1">
+      <c r="A86" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>E8</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>ប្រាក់ សុភារៈ</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>10H12BFGHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="25.2" customHeight="1">
+      <c r="A87" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>ED1</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>ឆេង សុជាតា</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>7A9AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="25.2" customHeight="1">
+      <c r="A88" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>ED2</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>នាង ជំនិត</t>
+        </is>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>8C11CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="25.2" customHeight="1">
+      <c r="A89" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>ED3</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>សួស  សុខឃៀង</t>
+        </is>
+      </c>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>10BCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="25.2" customHeight="1">
+      <c r="A90" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>ED4</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>ម៉ង់ ប៊ុនណារិទ្ធ</t>
+        </is>
+      </c>
+      <c r="D90" s="12" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>10EG11A</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="31.8" customHeight="1">
+      <c r="A91" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>ED5</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>សុខា សាមឌី</t>
+        </is>
+      </c>
+      <c r="D91" s="12" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E91" s="13" t="inlineStr">
+        <is>
+          <t>7BC9B</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="31.8" customHeight="1">
+      <c r="A92" s="5" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>ED6</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>ជៀស ឌីនីន</t>
+        </is>
+      </c>
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E92" s="13" t="inlineStr">
+        <is>
+          <t>7D10I11I</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="31.8" customHeight="1">
+      <c r="A93" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>ED7</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>ផន សុផារិទ្ធ</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E93" s="13" t="inlineStr">
+        <is>
+          <t>8BD10F</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="31.8" customHeight="1">
+      <c r="A94" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>ED8</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>មៀច ដាវណ្ណ</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E94" s="13" t="inlineStr">
+        <is>
+          <t>8A9C11F</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="31.8" customHeight="1">
+      <c r="A95" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>ED9</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>ផន ពុទ្ធាវី</t>
+        </is>
+      </c>
+      <c r="D95" s="12" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E95" s="13" t="inlineStr">
+        <is>
+          <t>8B10AH</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="31.8" customHeight="1">
+      <c r="A96" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>ED10</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>ផាត់ ចាន់សុផាន់ណា</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E96" s="13" t="inlineStr">
+        <is>
+          <t>10B11DG</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="31.8" customHeight="1">
+      <c r="A97" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>ED11</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>ឌុច វិសាល</t>
+        </is>
+      </c>
+      <c r="D97" s="12" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E97" s="13" t="inlineStr">
+        <is>
+          <t>11H</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="31.8" customHeight="1">
+      <c r="A98" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>AG1</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>ជុំ សុផន</t>
+        </is>
+      </c>
+      <c r="D98" s="12" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E98" s="13" t="inlineStr">
+        <is>
+          <t>7A8ABD10AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="31.8" customHeight="1">
+      <c r="A99" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>AG2</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>ងួន គ្រីន</t>
+        </is>
+      </c>
+      <c r="D99" s="12" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E99" s="13" t="inlineStr">
+        <is>
+          <t>7B8C10FH</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="31.8" customHeight="1">
+      <c r="A100" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>AG3</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>ចេង ចំរើន</t>
+        </is>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E100" s="13" t="inlineStr">
+        <is>
+          <t>9C10CD11I</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="31.8" customHeight="1">
+      <c r="A101" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>AG4</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>ឡេង សេស</t>
+        </is>
+      </c>
+      <c r="D101" s="12" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E101" s="13" t="inlineStr">
+        <is>
+          <t>7CD9AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="31.8" customHeight="1">
+      <c r="A102" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>AG5</t>
+        </is>
+      </c>
+      <c r="C102" s="11" t="inlineStr">
+        <is>
+          <t>លី ហួត</t>
+        </is>
+      </c>
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E102" s="13" t="inlineStr">
+        <is>
+          <t>7E9D10EI11AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="25.2" customHeight="1">
+      <c r="A103" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>AG6</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>ហុង សំអឿន</t>
+        </is>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>10G11CEH</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="31.8" customHeight="1">
+      <c r="A104" s="5" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>AG7</t>
+        </is>
+      </c>
+      <c r="C104" s="14" t="inlineStr">
+        <is>
+          <t>ជឹម នី</t>
+        </is>
+      </c>
+      <c r="D104" s="14" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E104" s="13" t="inlineStr">
+        <is>
+          <t>10B11FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="31.8" customHeight="1">
+      <c r="A105" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>AG8</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>សឿន សម្បត្តិ</t>
+        </is>
+      </c>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E105" s="13" t="inlineStr">
+        <is>
+          <t>9C11DFG</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="25.2" customHeight="1">
+      <c r="A106" s="5" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>Lib</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>កង សុគង់</t>
+        </is>
+      </c>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="n"/>
+    </row>
+    <row r="107" ht="25.2" customHeight="1">
+      <c r="A107" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>Lib</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>ស៊ិន ម៉ូនីដា</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="n"/>
+    </row>
+    <row r="108" ht="25.2" customHeight="1">
+      <c r="A108" s="5" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>Lib</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>សូ វណ្ណៈ</t>
+        </is>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E108" s="8" t="n"/>
+    </row>
+    <row r="109" ht="25.2" customHeight="1">
+      <c r="A109" s="5" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>យុវជន</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>ពេជ្រ និស្សិត</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E109" s="8" t="n"/>
+    </row>
+    <row r="110" ht="25.2" customHeight="1">
+      <c r="A110" s="5" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>លេខា</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>ទុន វណ្ណៈ</t>
+        </is>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E110" s="8" t="n"/>
+    </row>
+    <row r="111" ht="25.2" customHeight="1">
+      <c r="A111" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>គណនេយ្យ</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>ទូច សុខម៉េត</t>
+        </is>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E111" s="8" t="n"/>
+    </row>
+    <row r="112" ht="25.2" customHeight="1">
+      <c r="A112" s="5" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>នាយក</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>ផេង រិទ្ធីយ៉ា</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E112" s="8" t="n"/>
+    </row>
+    <row r="113" ht="25.2" customHeight="1">
+      <c r="A113" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>នាយករង</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>សុន  សុមនី</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E113" s="8" t="n"/>
+    </row>
+    <row r="114" ht="25.2" customHeight="1">
+      <c r="A114" s="5" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>នាយករង</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>ទិន សុភី</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E114" s="8" t="n"/>
+    </row>
+    <row r="115" ht="31.8" customHeight="1">
+      <c r="A115" s="5" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="15" t="inlineStr">
+        <is>
+          <t>នាយករង</t>
+        </is>
+      </c>
+      <c r="C115" s="16" t="inlineStr">
+        <is>
+          <t>ប៊ុន ណារី</t>
+        </is>
+      </c>
+      <c r="D115" s="17" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="E115" s="13" t="n"/>
+    </row>
+    <row r="116" ht="31.8" customHeight="1">
+      <c r="A116" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="15" t="inlineStr">
+        <is>
+          <t>នាយករង</t>
+        </is>
+      </c>
+      <c r="C116" s="18" t="inlineStr">
+        <is>
+          <t>ម៉ែន និមល</t>
+        </is>
+      </c>
+      <c r="D116" s="19" t="inlineStr">
+        <is>
+          <t>ប</t>
+        </is>
+      </c>
+      <c r="E116" s="13" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
